--- a/artfynd/A 53312-2025 artfynd.xlsx
+++ b/artfynd/A 53312-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125332658</v>
+        <v>56219583</v>
       </c>
       <c r="B2" t="n">
-        <v>91228</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Granryggen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455056</v>
+        <v>454971</v>
       </c>
       <c r="R2" t="n">
-        <v>7097270</v>
+        <v>7097475</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2014-09-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2014-09-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,29 +754,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125332652</v>
+        <v>125332658</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,27 +787,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454997</v>
+        <v>455056</v>
       </c>
       <c r="R3" t="n">
-        <v>7097432</v>
+        <v>7097270</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,17 +852,13 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,49 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125332645</v>
+        <v>56219584</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granryggen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455036</v>
+        <v>454920</v>
       </c>
       <c r="R4" t="n">
-        <v>7097458</v>
+        <v>7097433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,17 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2014-09-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2014-09-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,15 +962,332 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125334618</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Granryggen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>455245</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7097128</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Erik Söderhjelm</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Erik Söderhjelm</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125332645</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Granryggen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>455036</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7097458</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125332652</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Granryggen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>454997</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7097432</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53312-2025 artfynd.xlsx
+++ b/artfynd/A 53312-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56219583</t>
         </is>
       </c>
     </row>
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125332658</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56219584</t>
         </is>
       </c>
     </row>
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125334618</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125332645</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,8 +1318,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125332652</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>